--- a/output/pdf_financials_xlsx/ROAR.xlsx
+++ b/output/pdf_financials_xlsx/ROAR.xlsx
@@ -1306,7 +1306,7 @@
         <v>1.281541</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.756007</v>
+        <v>-0.756007</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-0.319439</v>
@@ -1349,19 +1349,19 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.021</v>
+        <v>-0.441796</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.334</v>
+        <v>-4.097252</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.32145</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0.02455</v>
+        <v>-2.461396</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.563082</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1597,22 +1597,22 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.231398</v>
+        <v>-0.231398</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.881626</v>
+        <v>-1.881626</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.660725</v>
+        <v>-0.660725</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.218423</v>
+        <v>-1.218423</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.281541</v>
+        <v>-1.281541</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.756007</v>
+        <v>-0.756007</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-0.319439</v>
@@ -1771,22 +1771,22 @@
         <v>-1.012161</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.231398</v>
+        <v>-0.231398</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.881626</v>
+        <v>-1.881626</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.660725</v>
+        <v>-0.660725</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.218423</v>
+        <v>-1.218423</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.281541</v>
+        <v>-1.281541</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.756007</v>
+        <v>-0.756007</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-0.319439</v>
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-9.903295</v>
+        <v>9.903295</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-22.024167</v>
+        <v>22.024167</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-40.6141</v>
+        <v>40.6141</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-64.07705</v>
+        <v>64.07705</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>1.281541</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.756007</v>
+        <v>-0.756007</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.319439</v>
@@ -2144,7 +2144,7 @@
         <v>1.281541</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.756007</v>
+        <v>-0.756007</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.319439</v>
@@ -2279,22 +2279,22 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>9.981083470375193</v>
+        <v>209.9810834703752</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>15.07474636964903</v>
+        <v>184.925253630351</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.975103240376098</v>
+        <v>198.0248967596239</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -5940,37 +5940,37 @@
         <v>0.81847</v>
       </c>
       <c r="D92" s="3" t="n">
+        <v>0.81847</v>
+      </c>
+      <c r="E92" s="3" t="n">
         <v>0.918195</v>
       </c>
-      <c r="E92" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.963095</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.00518</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.00131</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.00131</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.209195</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.42425</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.42425</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.42425</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.42425</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -5979,10 +5979,10 @@
         <v>0</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.038936</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.951853</v>
       </c>
     </row>
     <row r="93">
@@ -7465,7 +7465,7 @@
         <v>0.129978</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>5.327047</v>
+        <v>4.762318</v>
       </c>
     </row>
     <row r="119">
@@ -9906,7 +9906,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10603,7 +10607,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11114,7 +11122,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -11993,7 +12005,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -13415,7 +13431,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -15021,7 +15041,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -17257,7 +17281,11 @@
           <t>Share-based payments reserve 963,095</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -21774,7 +21802,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -42513,10 +42545,10 @@
         </is>
       </c>
       <c r="O340" s="5" t="n">
-        <v>1.281541</v>
+        <v>-1.281541</v>
       </c>
       <c r="P340" s="5" t="n">
-        <v>0.756007</v>
+        <v>-0.756007</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -43675,19 +43707,19 @@
         </is>
       </c>
       <c r="K352" s="5" t="n">
-        <v>0.231398</v>
+        <v>-0.231398</v>
       </c>
       <c r="L352" s="5" t="n">
-        <v>1.881626</v>
+        <v>-1.881626</v>
       </c>
       <c r="M352" s="5" t="n">
-        <v>0.660725</v>
+        <v>-0.660725</v>
       </c>
       <c r="N352" s="5" t="n">
-        <v>1.218423</v>
+        <v>-1.218423</v>
       </c>
       <c r="O352" s="5" t="n">
-        <v>1.281541</v>
+        <v>-1.281541</v>
       </c>
       <c r="P352" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ROAR.xlsx
+++ b/output/pdf_financials_xlsx/ROAR.xlsx
@@ -1041,37 +1041,37 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.02471</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.009313</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005243</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000674</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000157</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>2e-05</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-2e-06</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1995,37 +1995,37 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.980112</v>
+        <v>-1.004822</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.990813</v>
+        <v>-3.000126</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.532206</v>
+        <v>-2.537449</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.647892</v>
+        <v>-0.648566</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.557998</v>
+        <v>-0.558155</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.012161</v>
+        <v>-1.012166</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.210398</v>
+        <v>0.210393</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2.215626</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.660725</v>
+        <v>0.660705</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>1.242973</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.281541</v>
+        <v>1.281543</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.756007</v>
@@ -2111,37 +2111,37 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.980112</v>
+        <v>-1.004822</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.990813</v>
+        <v>-3.000126</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.532206</v>
+        <v>-2.537449</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.647892</v>
+        <v>-0.648566</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.557998</v>
+        <v>-0.558155</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.012161</v>
+        <v>-1.012166</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.214263</v>
+        <v>0.214258</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>2.215626</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.660725</v>
+        <v>0.660705</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>1.242973</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.281541</v>
+        <v>1.281543</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.756007</v>
@@ -2442,31 +2442,31 @@
         <v>0.001971</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.359498</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.078596</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.454408</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.163504</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.569785</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.239671</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.193143</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.869447</v>
       </c>
     </row>
     <row r="35">
@@ -2558,31 +2558,31 @@
         <v>0.001971</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.017598</v>
+        <v>0.377096</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.004017</v>
+        <v>0.08261300000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.454408</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.163504</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.569785</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.239671</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.193143</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.869447</v>
       </c>
     </row>
     <row r="37">
@@ -3254,31 +3254,31 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.639998</v>
+        <v>0.2805</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.177655</v>
+        <v>0.09905899999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.454408</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.165603</v>
+        <v>0.002099</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.581591</v>
+        <v>0.011806</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.361769</v>
+        <v>0.122098</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.309324</v>
+        <v>0.116181</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.404191</v>
+        <v>0.534744</v>
       </c>
     </row>
     <row r="49">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -42083,7 +42083,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -46811,7 +46811,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -48597,7 +48597,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -49906,7 +49906,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E415" s="5" t="n">

--- a/output/pdf_financials_xlsx/ROAR.xlsx
+++ b/output/pdf_financials_xlsx/ROAR.xlsx
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.132</v>
+        <v>-0.132</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.739</v>
+        <v>-0.739</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.51</v>
+        <v>-0.51</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -6449,22 +6449,22 @@
         <v>0</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.004395</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.001129</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.014057</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00513</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.015835</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.002456</v>
       </c>
       <c r="N101" s="3" t="n">
         <v>0</v>
@@ -6739,22 +6739,22 @@
         <v>0</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.117781</v>
+        <v>0.122176</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.035738</v>
+        <v>0.036867</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.844859</v>
+        <v>-0.858916</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.150287</v>
+        <v>0.145157</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.037461</v>
+        <v>-0.021626</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.119433</v>
+        <v>0.121889</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>-0.203685</v>
@@ -6986,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.013672</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.002192</v>
       </c>
       <c r="O110" s="3" t="n">
         <v>0</v>
@@ -7059,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.020967</v>
       </c>
     </row>
     <row r="112">
@@ -7255,13 +7255,13 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.072421</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.393836</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.083745</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.020967</v>
       </c>
     </row>
     <row r="135">
@@ -8489,7 +8489,7 @@
         <v>-0.890006</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-5.420961</v>
+        <v>-5.441928</v>
       </c>
     </row>
   </sheetData>
@@ -21701,7 +21701,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -22010,7 +22014,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -24967,7 +24975,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -26377,7 +26389,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -27054,7 +27070,11 @@
           <t>Proceeds from common shares issued for cash</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -29452,7 +29472,11 @@
           <t>HST/GST receivable</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -30624,7 +30648,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -50403,7 +50431,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E420" s="5" t="n">
         <v>0.132</v>
       </c>
